--- a/storage/app/category_list.xlsx
+++ b/storage/app/category_list.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -39,12 +39,6 @@
   </si>
   <si>
     <t>commission_rate</t>
-  </si>
-  <si>
-    <t>{"en":"Mobiles"}</t>
-  </si>
-  <si>
-    <t>mobiles</t>
   </si>
 </sst>
 </file>
@@ -384,7 +378,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -411,20 +405,6 @@
       </c>
       <c r="H1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
